--- a/tests/fixtures/excel_informes.xlsx
+++ b/tests/fixtures/excel_informes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>RIT</t>
   </si>
@@ -163,66 +163,77 @@
     <t>FAE Familia Sur</t>
   </si>
   <si>
-    <t>05/07/2026</t>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>25/07/2026</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>13/09/2026</t>
+  </si>
+  <si>
+    <t>04/08/2026</t>
   </si>
   <si>
     <t>20/07/2026</t>
   </si>
   <si>
-    <t>19/08/2026</t>
-  </si>
-  <si>
-    <t>08/09/2026</t>
-  </si>
-  <si>
-    <t>30/07/2026</t>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
   </si>
   <si>
     <t>15/07/2026</t>
   </si>
   <si>
-    <t>09/07/2026</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>23/08/2026</t>
-  </si>
-  <si>
-    <t>13/09/2025</t>
-  </si>
-  <si>
-    <t>05/06/2025</t>
-  </si>
-  <si>
-    <t>22/12/2025</t>
-  </si>
-  <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>11/04/2026</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>02/11/2025</t>
-  </si>
-  <si>
-    <t>11/01/2026</t>
-  </si>
-  <si>
-    <t>02/12/2025</t>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>18/09/2025</t>
+  </si>
+  <si>
+    <t>10/06/2025</t>
+  </si>
+  <si>
+    <t>27/12/2025</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>16/04/2026</t>
+  </si>
+  <si>
+    <t>15/02/2026</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>16/01/2026</t>
+  </si>
+  <si>
+    <t>07/12/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -238,7 +249,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -246,12 +257,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,25 +579,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -612,7 +641,7 @@
         <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -635,7 +664,7 @@
         <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -658,7 +687,7 @@
         <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -681,7 +710,7 @@
         <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -704,7 +733,7 @@
         <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -723,8 +752,11 @@
       <c r="E8" t="s">
         <v>45</v>
       </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -744,10 +776,10 @@
         <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -767,10 +799,10 @@
         <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -790,10 +822,10 @@
         <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
